--- a/Result/profitability/6811.xlsx
+++ b/Result/profitability/6811.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM26"/>
+  <dimension ref="A1:AM27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3236,30 +3236,30 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2524</v>
+        <v>2627</v>
       </c>
       <c r="D23" t="n">
-        <v>2204</v>
+        <v>2299</v>
       </c>
       <c r="E23" t="n">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F23" t="n">
-        <v>12.66</v>
+        <v>12.5</v>
       </c>
       <c r="G23" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8.03%</t>
+          <t>7.86%</t>
         </is>
       </c>
       <c r="I23" t="n">
         <v>-9</v>
       </c>
       <c r="J23" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K23" t="n">
         <v>153</v>
@@ -3271,7 +3271,7 @@
         <v>3.325</v>
       </c>
       <c r="N23" t="n">
-        <v>13.14375</v>
+        <v>13.12375</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -3304,10 +3304,10 @@
         <v>-0.07730673316708225</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.6400000000000006</v>
+        <v>0.4800000000000004</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.0532445923460898</v>
+        <v>0.03993344425956735</v>
       </c>
       <c r="AA23" t="n">
         <v>0.02000000000000002</v>
@@ -3316,10 +3316,10 @@
         <v>0.005434782608695565</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.4000000000000004</v>
+        <v>-0.5600000000000005</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.03062787136294032</v>
+        <v>-0.04287901990811638</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3363,30 +3363,30 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2200</v>
+        <v>2097</v>
       </c>
       <c r="D24" t="n">
-        <v>1896</v>
+        <v>1802</v>
       </c>
       <c r="E24" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F24" t="n">
-        <v>13.81</v>
+        <v>14.07</v>
       </c>
       <c r="G24" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8.10%</t>
+          <t>8.31%</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K24" t="n">
         <v>147</v>
@@ -3398,7 +3398,7 @@
         <v>3.3575</v>
       </c>
       <c r="N24" t="n">
-        <v>13.0725</v>
+        <v>13.085</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -3431,10 +3431,10 @@
         <v>-0.04054054054054068</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.0908372827804107</v>
+        <v>0.1255999999999999</v>
       </c>
       <c r="AA24" t="n">
         <v>0.1699999999999999</v>
@@ -3443,10 +3443,10 @@
         <v>0.0502958579881656</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.7400000000000002</v>
+        <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.05661820964039777</v>
+        <v>0.07651109410864576</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3525,13 +3525,13 @@
         <v>3.42125</v>
       </c>
       <c r="N25" t="n">
-        <v>12.69</v>
+        <v>12.7025</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3558,10 +3558,10 @@
         <v>-0.1239436619718309</v>
       </c>
       <c r="Y25" t="n">
-        <v>-2.380000000000001</v>
+        <v>-2.640000000000001</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.1723388848660391</v>
+        <v>-0.187633262260128</v>
       </c>
       <c r="AA25" t="n">
         <v>0.6199999999999997</v>
@@ -3652,7 +3652,7 @@
         <v>3.59</v>
       </c>
       <c r="N26" t="n">
-        <v>12.61125</v>
+        <v>12.62375</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -3730,6 +3730,133 @@
       </c>
       <c r="AM26" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6811</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2967</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2598</v>
+      </c>
+      <c r="E27" t="n">
+        <v>369</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>240</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>8.08%</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>243</v>
+      </c>
+      <c r="K27" t="n">
+        <v>194</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.71625</v>
+      </c>
+      <c r="N27" t="n">
+        <v>12.54625</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.02291666666666659</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.005658852061438902</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.9900000000000002</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.2675675675675677</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.0600000000000005</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.004800000000000026</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
